--- a/templates/YesBank/YesBank_Repossesion_Template_2026-27.xlsx
+++ b/templates/YesBank/YesBank_Repossesion_Template_2026-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\YesBank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C5724A-AB66-47F2-9FF3-D6BE28F82B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE508B-6B17-415D-AE9D-3794F268194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26FBB636-9C2E-4FAA-9547-F3807627EF54}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="191">
   <si>
     <t>YES Bank Repo Agency Audit</t>
   </si>
@@ -629,7 +629,7 @@
     <t>Repossesion</t>
   </si>
   <si>
-    <t>KGAC</t>
+    <t>Kumar Gaurav Agarwal &amp; Company</t>
   </si>
 </sst>
 </file>
@@ -825,7 +825,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1087,6 +1087,19 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1104,7 +1117,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1531,6 +1544,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1543,12 +1565,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="_Amar's Vehicle_Audit_Report_auto_july_agt_06_Nasik Auto Jan. 07_cv_PIVOT 1_SERIES 2" xfId="8" xr:uid="{769AE058-3E60-4935-A451-AE88C81DA2CF}"/>
@@ -1938,7 +1955,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51899D29-7097-486E-942D-3E267DC0F113}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B2:K30"/>
+  <dimension ref="B2:K31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.3984375" style="2" customWidth="1"/>
@@ -1952,360 +1969,363 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="139"/>
-    </row>
-    <row r="3" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="142"/>
+    </row>
+    <row r="3" spans="2:11" s="143" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="11" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="140" t="s">
+      <c r="G7" s="137" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="11" t="s">
+    <row r="8" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="18" t="s">
+      <c r="E9" s="138" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="141" t="s">
+      <c r="C10" s="136" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="19"/>
       <c r="F10" s="20"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
-        <v>16</v>
-      </c>
+      <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="136" t="s">
+      <c r="B13" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="136" t="s">
+      <c r="C14" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="136" t="s">
+      <c r="D14" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="136" t="s">
+      <c r="E14" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="136" t="s">
+      <c r="F14" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="139"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f>Agency!J20</f>
         <v>40</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D16" s="29">
         <v>40</v>
       </c>
-      <c r="E15" s="30">
-        <f>C15/D15</f>
+      <c r="E16" s="30">
+        <f>C16/D16</f>
         <v>1</v>
       </c>
-      <c r="F15" s="31"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="28" t="s">
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f>Agency!J26</f>
         <v>40</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D17" s="29">
         <v>40</v>
       </c>
-      <c r="E16" s="30">
-        <f t="shared" ref="E16:E18" si="0">C16/D16</f>
+      <c r="E17" s="30">
+        <f t="shared" ref="E17:E19" si="0">C17/D17</f>
         <v>1</v>
       </c>
-      <c r="F16" s="31"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="28" t="s">
+      <c r="F17" s="31"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f>Agency!J36</f>
         <v>20</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D18" s="29">
         <v>20</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E18" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F17" s="31"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="28" t="s">
+      <c r="F18" s="31"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="32">
-        <f>SUM(C15:C17)</f>
+      <c r="C19" s="32">
+        <f>SUM(C16:C18)</f>
         <v>100</v>
       </c>
-      <c r="D18" s="32">
-        <f>SUM(D15:D17)</f>
+      <c r="D19" s="32">
+        <f>SUM(D16:D18)</f>
         <v>100</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E19" s="33">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F18" s="136" t="str">
-        <f>IF(ROUNDUP(E18,2)&lt;60%,"C",IF(ROUNDUP(E18,2)&lt;70%,"C+",IF(ROUNDUP(E18,2)&lt;80%,"B",IF(ROUNDUP(E18,2)&lt;90%,"B+",IF(ROUNDUP(E18,2)&lt;100%,"A","A+")))))</f>
+      <c r="F19" s="139" t="str">
+        <f>IF(ROUNDUP(E19,2)&lt;60%,"C",IF(ROUNDUP(E19,2)&lt;70%,"C+",IF(ROUNDUP(E19,2)&lt;80%,"B",IF(ROUNDUP(E19,2)&lt;90%,"B+",IF(ROUNDUP(E19,2)&lt;100%,"A","A+")))))</f>
         <v>A+</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="28" t="s">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="136" t="str">
-        <f>VLOOKUP($F$18,$C$24:$D$30,2,FALSE)</f>
+      <c r="C20" s="139" t="str">
+        <f>VLOOKUP($F$19,$C$25:$D$31,2,FALSE)</f>
         <v>Excellent</v>
       </c>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="34" t="s">
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="28" t="s">
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D25" s="28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="35">
         <v>100</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C26" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D26" s="37" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C31" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D31" s="37" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="C7">
     <cfRule type="expression" dxfId="5" priority="5">
+      <formula>OR($V7="Excluded",$V7="Audit Failed")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>$V7="Audited"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>OR($V6="Excluded",$V6="Audit Failed")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$V6="Audited"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>OR($V5="Excluded",$V5="Audit Failed")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>$V5="Audited"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G8">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>OR($V7="Excluded",$V7="Audit Failed")</formula>
+      <formula>OR($V8="Excluded",$V8="Audit Failed")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$V7="Audited"</formula>
+      <formula>$V8="Audited"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/YesBank/YesBank_Repossesion_Template_2026-27.xlsx
+++ b/templates/YesBank/YesBank_Repossesion_Template_2026-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\YesBank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE508B-6B17-415D-AE9D-3794F268194E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CF3791-C1AA-4FBB-B569-A773B7A58B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26FBB636-9C2E-4FAA-9547-F3807627EF54}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="192">
   <si>
     <t>YES Bank Repo Agency Audit</t>
   </si>
@@ -630,6 +630,9 @@
   </si>
   <si>
     <t>Kumar Gaurav Agarwal &amp; Company</t>
+  </si>
+  <si>
+    <t>Sr. No</t>
   </si>
 </sst>
 </file>
@@ -825,7 +828,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1098,6 +1101,21 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1117,7 +1135,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1136,41 +1154,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1553,6 +1547,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1565,7 +1564,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="_Amar's Vehicle_Audit_Report_auto_july_agt_06_Nasik Auto Jan. 07_cv_PIVOT 1_SERIES 2" xfId="8" xr:uid="{769AE058-3E60-4935-A451-AE88C81DA2CF}"/>
@@ -1969,16 +1985,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="142"/>
-    </row>
-    <row r="3" spans="2:11" s="143" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136"/>
+    </row>
+    <row r="3" spans="2:11" s="131" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
@@ -1994,302 +2010,302 @@
       <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="139"/>
       <c r="F6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="142"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="138"/>
+      <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="11" t="s">
+      <c r="E7" s="140"/>
+      <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="137" t="s">
+      <c r="G7" s="129" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="11" t="s">
+      <c r="C8" s="130"/>
+      <c r="D8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="130"/>
+      <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="141"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="11" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="138" t="s">
+      <c r="E9" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="136" t="s">
+      <c r="C10" s="128" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="12"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="22"/>
+      <c r="D11" s="14"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="20"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="139" t="s">
+      <c r="D14" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="139" t="s">
+      <c r="E14" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="139" t="s">
+      <c r="F14" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="21">
         <f>Agency!J20</f>
         <v>40</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="21">
         <v>40</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="22">
         <f>C16/D16</f>
         <v>1</v>
       </c>
-      <c r="F16" s="31"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="21">
         <f>Agency!J26</f>
         <v>40</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="21">
         <v>40</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="22">
         <f t="shared" ref="E17:E19" si="0">C17/D17</f>
         <v>1</v>
       </c>
-      <c r="F17" s="31"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="21">
         <f>Agency!J36</f>
         <v>20</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="21">
         <v>20</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F18" s="31"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="24">
         <f>SUM(C16:C18)</f>
         <v>100</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="24">
         <f>SUM(D16:D18)</f>
         <v>100</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F19" s="139" t="str">
+      <c r="F19" s="133" t="str">
         <f>IF(ROUNDUP(E19,2)&lt;60%,"C",IF(ROUNDUP(E19,2)&lt;70%,"C+",IF(ROUNDUP(E19,2)&lt;80%,"B",IF(ROUNDUP(E19,2)&lt;90%,"B+",IF(ROUNDUP(E19,2)&lt;100%,"A","A+")))))</f>
         <v>A+</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="139" t="str">
+      <c r="C20" s="133" t="str">
         <f>VLOOKUP($F$19,$C$25:$D$31,2,FALSE)</f>
         <v>Excellent</v>
       </c>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="35">
+      <c r="B26" s="27">
         <v>100</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="29" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2339,1463 +2355,1463 @@
   <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultColWidth="18.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.8984375" style="82" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.8984375" style="65" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.59765625" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" style="65" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.3984375" style="65" customWidth="1"/>
-    <col min="7" max="7" width="16.3984375" style="65" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" style="65" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.19921875" style="65" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.59765625" style="65" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.3984375" style="65" customWidth="1"/>
-    <col min="12" max="12" width="44.59765625" style="65" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" style="65" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.09765625" style="65" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.3984375" style="65" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="18.8984375" style="65"/>
+    <col min="1" max="1" width="5.8984375" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.8984375" style="57" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.59765625" style="57" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" style="57" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.3984375" style="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.3984375" style="57" customWidth="1"/>
+    <col min="7" max="7" width="16.3984375" style="57" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.19921875" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.59765625" style="57" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.3984375" style="57" customWidth="1"/>
+    <col min="12" max="12" width="44.59765625" style="57" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="57" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.09765625" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.3984375" style="57" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="18.8984375" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:15" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="40" t="s">
+      <c r="J1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="42" t="s">
+      <c r="M1" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="42" t="s">
+      <c r="N1" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="O1" s="35" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="84">
+    <row r="2" spans="1:15" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="76">
         <v>1</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="90" t="s">
+      <c r="F2" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="91" t="s">
+      <c r="G2" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="I2" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="116">
+      <c r="J2" s="108">
         <f>IF(H2="NA","NA",IF(H2="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="M2" s="48"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="50"/>
-    </row>
-    <row r="3" spans="1:15" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="84">
+      <c r="M2" s="40"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="3" spans="1:15" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="76">
         <v>2</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="89" t="s">
+      <c r="E3" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="90" t="s">
+      <c r="F3" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="91" t="s">
+      <c r="G3" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="92" t="s">
+      <c r="H3" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="116">
+      <c r="J3" s="108">
         <f>IF(H3="NA","NA",IF(H3="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="47" t="s">
+      <c r="K3" s="38"/>
+      <c r="L3" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="50"/>
-    </row>
-    <row r="4" spans="1:15" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="84">
+      <c r="M3" s="40"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="42"/>
+    </row>
+    <row r="4" spans="1:15" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A4" s="76">
         <v>3</v>
       </c>
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="C4" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="E4" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="91" t="s">
+      <c r="G4" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="92" t="s">
+      <c r="H4" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="93" t="s">
+      <c r="I4" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="116">
+      <c r="J4" s="108">
         <f>IF(H4="NA","NA",IF(H4="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="47" t="s">
+      <c r="K4" s="38"/>
+      <c r="L4" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="50"/>
-    </row>
-    <row r="5" spans="1:15" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="84">
+      <c r="M4" s="40"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="42"/>
+    </row>
+    <row r="5" spans="1:15" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="76">
         <v>4</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="89" t="s">
+      <c r="C5" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="89" t="s">
+      <c r="E5" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="90" t="s">
+      <c r="F5" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="91" t="s">
+      <c r="G5" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="93" t="s">
+      <c r="I5" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="116">
+      <c r="J5" s="108">
         <f>IF(H5="NA","NA",IF(H5="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K5" s="46"/>
-      <c r="L5" s="47" t="s">
+      <c r="K5" s="38"/>
+      <c r="L5" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="M5" s="48"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="50"/>
-    </row>
-    <row r="6" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="84">
+      <c r="M5" s="40"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="42"/>
+    </row>
+    <row r="6" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="76">
         <v>5</v>
       </c>
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="89" t="s">
+      <c r="C6" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="89" t="s">
+      <c r="E6" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="95" t="s">
+      <c r="F6" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="89" t="s">
+      <c r="G6" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="92" t="s">
+      <c r="H6" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="92" t="s">
+      <c r="I6" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="116">
+      <c r="J6" s="108">
         <f t="shared" ref="J6:J15" si="0">IF(H6="NA","NA",IF(H6="Yes",10,IF(I6=1,8,IF(I6=2,6,IF(I6=3,4,IF(I6=4,2,IF(I6&gt;=4,0)))))))</f>
         <v>10</v>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="52" t="s">
+      <c r="K6" s="37"/>
+      <c r="L6" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M6" s="45"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="50"/>
-    </row>
-    <row r="7" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="84">
+      <c r="M6" s="37"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="42"/>
+    </row>
+    <row r="7" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="76">
         <v>6</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="F7" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="89" t="s">
+      <c r="G7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="92" t="s">
+      <c r="H7" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="92" t="s">
+      <c r="I7" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="116">
+      <c r="J7" s="108">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K7" s="45"/>
-      <c r="L7" s="52" t="s">
+      <c r="K7" s="37"/>
+      <c r="L7" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M7" s="45"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="50"/>
-    </row>
-    <row r="8" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="84">
+      <c r="M7" s="37"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="42"/>
+    </row>
+    <row r="8" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="76">
         <v>7</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="F8" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="89" t="s">
+      <c r="G8" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="92" t="s">
+      <c r="H8" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="92" t="s">
+      <c r="I8" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J8" s="116" t="str">
+      <c r="J8" s="108" t="str">
         <f t="shared" si="0"/>
         <v>NA</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="52" t="s">
+      <c r="K8" s="37"/>
+      <c r="L8" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M8" s="45"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="50"/>
-    </row>
-    <row r="9" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="84">
+      <c r="M8" s="37"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="42"/>
+    </row>
+    <row r="9" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="76">
         <v>8</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="89" t="s">
+      <c r="C9" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="95" t="s">
+      <c r="F9" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="89" t="s">
+      <c r="G9" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="92" t="s">
+      <c r="H9" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="92" t="s">
+      <c r="I9" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="116" t="str">
+      <c r="J9" s="108" t="str">
         <f t="shared" si="0"/>
         <v>NA</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="52" t="s">
+      <c r="K9" s="37"/>
+      <c r="L9" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M9" s="45"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="50"/>
-    </row>
-    <row r="10" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="84">
+      <c r="M9" s="37"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="42"/>
+    </row>
+    <row r="10" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="76">
         <v>9</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="89" t="s">
+      <c r="C10" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="E10" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="95" t="s">
+      <c r="F10" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="89" t="s">
+      <c r="G10" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="92" t="s">
+      <c r="H10" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="92" t="s">
+      <c r="I10" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="116" t="str">
+      <c r="J10" s="108" t="str">
         <f t="shared" si="0"/>
         <v>NA</v>
       </c>
-      <c r="K10" s="45"/>
-      <c r="L10" s="52" t="s">
+      <c r="K10" s="37"/>
+      <c r="L10" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M10" s="45"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="50"/>
-    </row>
-    <row r="11" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="84">
+      <c r="M10" s="37"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="42"/>
+    </row>
+    <row r="11" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="76">
         <v>10</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="89" t="s">
+      <c r="D11" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="89" t="s">
+      <c r="G11" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="92" t="s">
+      <c r="H11" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="92" t="s">
+      <c r="I11" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="116">
+      <c r="J11" s="108">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K11" s="45"/>
-      <c r="L11" s="52" t="s">
+      <c r="K11" s="37"/>
+      <c r="L11" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M11" s="45"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="50"/>
-    </row>
-    <row r="12" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="84">
+      <c r="M11" s="37"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="42"/>
+    </row>
+    <row r="12" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="76">
         <v>11</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C12" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="89" t="s">
+      <c r="D12" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="89" t="s">
+      <c r="E12" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="95" t="s">
+      <c r="F12" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="89" t="s">
+      <c r="G12" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="92" t="s">
+      <c r="H12" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="92" t="s">
+      <c r="I12" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="116" t="str">
+      <c r="J12" s="108" t="str">
         <f t="shared" si="0"/>
         <v>NA</v>
       </c>
-      <c r="K12" s="45"/>
-      <c r="L12" s="52" t="s">
+      <c r="K12" s="37"/>
+      <c r="L12" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M12" s="45"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="50"/>
-    </row>
-    <row r="13" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="84">
+      <c r="M12" s="37"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="42"/>
+    </row>
+    <row r="13" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="76">
         <v>12</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="95" t="s">
+      <c r="F13" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="92" t="s">
+      <c r="H13" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="92" t="s">
+      <c r="I13" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="116">
+      <c r="J13" s="108">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K13" s="45"/>
-      <c r="L13" s="52" t="s">
+      <c r="K13" s="37"/>
+      <c r="L13" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M13" s="45"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="50"/>
-    </row>
-    <row r="14" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="84">
+      <c r="M13" s="37"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="42"/>
+    </row>
+    <row r="14" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="76">
         <v>13</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="89" t="s">
+      <c r="D14" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="89" t="s">
+      <c r="E14" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="95" t="s">
+      <c r="F14" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="89" t="s">
+      <c r="G14" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="92" t="s">
+      <c r="H14" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="92" t="s">
+      <c r="I14" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="116">
+      <c r="J14" s="108">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K14" s="45"/>
-      <c r="L14" s="52" t="s">
+      <c r="K14" s="37"/>
+      <c r="L14" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M14" s="45"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="50"/>
-    </row>
-    <row r="15" spans="1:15" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="84">
+      <c r="M14" s="37"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="42"/>
+    </row>
+    <row r="15" spans="1:15" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="76">
         <v>14</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="89" t="s">
+      <c r="D15" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="89" t="s">
+      <c r="E15" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="95" t="s">
+      <c r="F15" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="89" t="s">
+      <c r="G15" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="92" t="s">
+      <c r="H15" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="92" t="s">
+      <c r="I15" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="116">
+      <c r="J15" s="108">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="52" t="s">
+      <c r="K15" s="37"/>
+      <c r="L15" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="50"/>
-    </row>
-    <row r="16" spans="1:15" s="51" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A16" s="84">
+      <c r="M15" s="37"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="42"/>
+    </row>
+    <row r="16" spans="1:15" s="43" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A16" s="76">
         <v>15</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="96" t="s">
+      <c r="C16" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="96" t="s">
+      <c r="D16" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="89" t="s">
+      <c r="E16" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="97" t="s">
+      <c r="F16" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="91" t="s">
+      <c r="G16" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="93" t="s">
+      <c r="H16" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="93" t="s">
+      <c r="I16" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J16" s="117">
+      <c r="J16" s="109">
         <f>IF(H16="NA","NA",IF(H16="YES",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K16" s="55" t="s">
+      <c r="K16" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="L16" s="56" t="s">
+      <c r="L16" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="50"/>
-    </row>
-    <row r="17" spans="1:17" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="84">
+      <c r="M16" s="37"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="1:17" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="76">
         <v>16</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="C17" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="D17" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="89" t="s">
+      <c r="F17" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="99" t="s">
+      <c r="G17" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="92" t="s">
+      <c r="H17" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="92" t="s">
+      <c r="I17" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="116">
+      <c r="J17" s="108">
         <f>IF(H17="NA","NA",IF(H17="Yes",10,IF(I17=1,-5,-10)))</f>
         <v>10</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="56" t="s">
+      <c r="K17" s="37"/>
+      <c r="L17" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="50"/>
-    </row>
-    <row r="18" spans="1:17" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="84">
+      <c r="M17" s="37"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="42"/>
+    </row>
+    <row r="18" spans="1:17" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="76">
         <v>17</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="100" t="s">
+      <c r="C18" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="100" t="s">
+      <c r="D18" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="100" t="s">
+      <c r="E18" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="100" t="s">
+      <c r="F18" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="101" t="s">
+      <c r="G18" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="102" t="s">
+      <c r="H18" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="102" t="s">
+      <c r="I18" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="J18" s="118">
+      <c r="J18" s="110">
         <f>IF(H18="NA","NA",IF(H18="Yes",10,IF(I18=1,-5,IF(I18=2,-10,IF(I18=3,-15,-20)))))</f>
         <v>10</v>
       </c>
-      <c r="K18" s="57" t="s">
+      <c r="K18" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="56" t="s">
+      <c r="L18" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="M18" s="57"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="59"/>
-    </row>
-    <row r="19" spans="1:17" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="84">
+      <c r="M18" s="49"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="51"/>
+    </row>
+    <row r="19" spans="1:17" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A19" s="76">
         <v>18</v>
       </c>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="123" t="s">
+      <c r="F19" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="101" t="s">
+      <c r="G19" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="102" t="s">
+      <c r="H19" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="102" t="s">
+      <c r="I19" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="J19" s="118">
+      <c r="J19" s="110">
         <f>IF(H19="NA","NA",IF(H19="Yes",10,IF(I19=1,-5,IF(I19=2,-10,IF(I19=3,-15,-20)))))</f>
         <v>10</v>
       </c>
-      <c r="K19" s="57" t="s">
+      <c r="K19" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="L19" s="60" t="s">
+      <c r="L19" s="52" t="s">
         <v>172</v>
       </c>
-      <c r="M19" s="45"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="50"/>
-    </row>
-    <row r="20" spans="1:17" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="85" t="s">
+      <c r="M19" s="37"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="42"/>
+    </row>
+    <row r="20" spans="1:17" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="119">
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="111">
         <f>(SUM(J2:J19)/(COUNT(J2:J19)*10)*40)</f>
         <v>40</v>
       </c>
-      <c r="K20" s="61"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="65"/>
-      <c r="Q20" s="65"/>
-    </row>
-    <row r="21" spans="1:17" s="51" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A21" s="84">
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="56"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+    </row>
+    <row r="21" spans="1:17" s="43" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A21" s="76">
         <v>19</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="89" t="s">
+      <c r="C21" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="106" t="s">
+      <c r="E21" s="98" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="106" t="s">
+      <c r="F21" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="G21" s="89" t="s">
+      <c r="G21" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="H21" s="96" t="s">
+      <c r="H21" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="107" t="s">
+      <c r="I21" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="117">
+      <c r="J21" s="109">
         <f>IF(H21="NA","NA",IF(H21="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K21" s="54" t="s">
+      <c r="K21" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="L21" s="48" t="s">
+      <c r="L21" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="M21" s="48"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="50"/>
-    </row>
-    <row r="22" spans="1:17" s="51" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="84">
+      <c r="M21" s="40"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="42"/>
+    </row>
+    <row r="22" spans="1:17" s="43" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="76">
         <v>20</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="106" t="s">
+      <c r="E22" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="124" t="s">
+      <c r="F22" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="89" t="s">
+      <c r="G22" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="96" t="s">
+      <c r="H22" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="I22" s="107" t="s">
+      <c r="I22" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="J22" s="117">
+      <c r="J22" s="109">
         <f>IF(H22="NA","NA",IF(H22="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K22" s="54"/>
-      <c r="L22" s="48" t="s">
+      <c r="K22" s="46"/>
+      <c r="L22" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="M22" s="48"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="50"/>
-    </row>
-    <row r="23" spans="1:17" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="84">
+      <c r="M22" s="40"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="42"/>
+    </row>
+    <row r="23" spans="1:17" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="76">
         <v>21</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="89" t="s">
+      <c r="C23" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="D23" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="89" t="s">
+      <c r="E23" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="123" t="s">
+      <c r="F23" s="115" t="s">
         <v>113</v>
       </c>
-      <c r="G23" s="108" t="s">
+      <c r="G23" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="93" t="s">
+      <c r="H23" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J23" s="117">
+      <c r="J23" s="109">
         <f>IF(H23="NA","NA",IF(H23="Yes",10,IF(I23=1,8,IF(I23=2,6,IF(I23=3,4,IF(I23=4,2,0))))))</f>
         <v>10</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="56" t="s">
+      <c r="K23" s="46"/>
+      <c r="L23" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="M23" s="48"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="50"/>
-    </row>
-    <row r="24" spans="1:17" s="51" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="84">
+      <c r="M23" s="40"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="42"/>
+    </row>
+    <row r="24" spans="1:17" s="43" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="76">
         <v>22</v>
       </c>
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="89" t="s">
+      <c r="D24" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="89" t="s">
+      <c r="E24" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="F24" s="123" t="s">
+      <c r="F24" s="115" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="108" t="s">
+      <c r="G24" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="93" t="s">
+      <c r="H24" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="I24" s="93" t="s">
+      <c r="I24" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J24" s="117">
+      <c r="J24" s="109">
         <f>IF(H24="NA","NA",IF(H24="Yes",10,IF(I24=1,8,IF(I24=2,6,IF(I24=3,4,IF(I24=4,2,0))))))</f>
         <v>10</v>
       </c>
-      <c r="K24" s="54"/>
-      <c r="L24" s="56" t="s">
+      <c r="K24" s="46"/>
+      <c r="L24" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="M24" s="48"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="50"/>
-    </row>
-    <row r="25" spans="1:17" s="51" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A25" s="84">
+      <c r="M24" s="40"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="42"/>
+    </row>
+    <row r="25" spans="1:17" s="43" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A25" s="76">
         <v>23</v>
       </c>
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="96" t="s">
+      <c r="E25" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="F25" s="125" t="s">
+      <c r="F25" s="117" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="91" t="s">
+      <c r="G25" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="H25" s="93" t="s">
+      <c r="H25" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="93" t="s">
+      <c r="I25" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="J25" s="116" t="str">
+      <c r="J25" s="108" t="str">
         <f>IF(H25="NA","NA",IF(H25="Yes",10,-10))</f>
         <v>NA</v>
       </c>
-      <c r="K25" s="54" t="s">
+      <c r="K25" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="L25" s="67" t="s">
+      <c r="L25" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="50"/>
-    </row>
-    <row r="26" spans="1:17" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85" t="s">
+      <c r="M25" s="59"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="42"/>
+    </row>
+    <row r="26" spans="1:17" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="103"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="110" t="s">
+      <c r="B26" s="95"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="110"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="119">
+      <c r="F26" s="102"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="111">
         <f>(SUM(J21:J25)/(COUNT(J21:J25)*10)*40)</f>
         <v>40</v>
       </c>
-      <c r="K26" s="61"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-    </row>
-    <row r="27" spans="1:17" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A27" s="86">
+      <c r="K26" s="53"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+    </row>
+    <row r="27" spans="1:17" s="66" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A27" s="78">
         <v>24</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="100" t="s">
+      <c r="C27" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="100" t="s">
+      <c r="D27" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="100" t="s">
+      <c r="E27" s="92" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="G27" s="112" t="s">
+      <c r="G27" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="H27" s="113" t="s">
+      <c r="H27" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="I27" s="114" t="s">
+      <c r="I27" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J27" s="118">
+      <c r="J27" s="110">
         <f t="shared" ref="J27:J33" si="1">IF(H27="NA","NA",IF(H27="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K27" s="72" t="s">
+      <c r="K27" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="L27" s="73" t="s">
+      <c r="L27" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-    </row>
-    <row r="28" spans="1:17" s="74" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A28" s="84">
+      <c r="M27" s="59"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+    </row>
+    <row r="28" spans="1:17" s="66" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A28" s="76">
         <v>25</v>
       </c>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="100" t="s">
+      <c r="C28" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="100" t="s">
+      <c r="D28" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="115" t="s">
+      <c r="E28" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="F28" s="127" t="s">
+      <c r="F28" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="G28" s="112" t="s">
+      <c r="G28" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="H28" s="113" t="s">
+      <c r="H28" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="I28" s="114" t="s">
+      <c r="I28" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="118">
+      <c r="J28" s="110">
         <f>IF(H28="NA","NA",IF(H28="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K28" s="72" t="s">
+      <c r="K28" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="L28" s="56" t="s">
+      <c r="L28" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="M28" s="67"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-    </row>
-    <row r="29" spans="1:17" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A29" s="84">
+      <c r="M28" s="59"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+    </row>
+    <row r="29" spans="1:17" s="66" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A29" s="76">
         <v>26</v>
       </c>
-      <c r="B29" s="88" t="s">
+      <c r="B29" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="100" t="s">
+      <c r="C29" s="92" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="100" t="s">
+      <c r="D29" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="100" t="s">
+      <c r="E29" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="126" t="s">
+      <c r="F29" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="G29" s="101" t="s">
+      <c r="G29" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="H29" s="113" t="s">
+      <c r="H29" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="I29" s="102" t="s">
+      <c r="I29" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="J29" s="118">
+      <c r="J29" s="110">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K29" s="72"/>
-      <c r="L29" s="56" t="s">
+      <c r="K29" s="64"/>
+      <c r="L29" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="M29" s="67"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="59"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-    </row>
-    <row r="30" spans="1:17" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="84">
+      <c r="M29" s="59"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="51"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+    </row>
+    <row r="30" spans="1:17" s="66" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="76">
         <v>27</v>
       </c>
-      <c r="B30" s="88" t="s">
+      <c r="B30" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="100" t="s">
+      <c r="C30" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="100" t="s">
+      <c r="D30" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="100" t="s">
+      <c r="E30" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="F30" s="126" t="s">
+      <c r="F30" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="G30" s="101" t="s">
+      <c r="G30" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="H30" s="102" t="s">
+      <c r="H30" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="114" t="s">
+      <c r="I30" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J30" s="118">
+      <c r="J30" s="110">
         <f>IF(H30="NA","NA",IF(H30="yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K30" s="72"/>
-      <c r="L30" s="73" t="s">
+      <c r="K30" s="64"/>
+      <c r="L30" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="M30" s="67"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-    </row>
-    <row r="31" spans="1:17" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A31" s="84">
+      <c r="M30" s="59"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+    </row>
+    <row r="31" spans="1:17" s="66" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A31" s="76">
         <v>28</v>
       </c>
-      <c r="B31" s="88" t="s">
+      <c r="B31" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="100" t="s">
+      <c r="C31" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="100" t="s">
+      <c r="D31" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="100" t="s">
+      <c r="E31" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="126" t="s">
+      <c r="F31" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="G31" s="101" t="s">
+      <c r="G31" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="H31" s="102" t="s">
+      <c r="H31" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I31" s="114" t="s">
+      <c r="I31" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J31" s="118">
+      <c r="J31" s="110">
         <f>IF(H31="NA","NA",IF(H31="yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K31" s="72" t="s">
+      <c r="K31" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="L31" s="75" t="s">
+      <c r="L31" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="M31" s="67"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-    </row>
-    <row r="32" spans="1:17" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A32" s="84">
+      <c r="M31" s="59"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+    </row>
+    <row r="32" spans="1:17" s="66" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A32" s="76">
         <v>29</v>
       </c>
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="100" t="s">
+      <c r="C32" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="100" t="s">
+      <c r="D32" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="100" t="s">
+      <c r="E32" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="F32" s="126" t="s">
+      <c r="F32" s="118" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="101" t="s">
+      <c r="G32" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="H32" s="102" t="s">
+      <c r="H32" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I32" s="114" t="s">
+      <c r="I32" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="118">
+      <c r="J32" s="110">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K32" s="57" t="s">
+      <c r="K32" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="L32" s="75" t="s">
+      <c r="L32" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="M32" s="67"/>
-      <c r="N32" s="68"/>
-      <c r="O32" s="59"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-    </row>
-    <row r="33" spans="1:17" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A33" s="84">
+      <c r="M32" s="59"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+    </row>
+    <row r="33" spans="1:17" s="66" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="76">
         <v>30</v>
       </c>
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="100" t="s">
+      <c r="C33" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="100" t="s">
+      <c r="D33" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="100" t="s">
+      <c r="E33" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="F33" s="126" t="s">
+      <c r="F33" s="118" t="s">
         <v>137</v>
       </c>
-      <c r="G33" s="112" t="s">
+      <c r="G33" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="H33" s="113" t="s">
+      <c r="H33" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="I33" s="114" t="s">
+      <c r="I33" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J33" s="118">
+      <c r="J33" s="110">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="L33" s="75" t="s">
+      <c r="L33" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="M33" s="45"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="59"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-    </row>
-    <row r="34" spans="1:17" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A34" s="84">
+      <c r="M33" s="37"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="51"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+    </row>
+    <row r="34" spans="1:17" s="66" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="76">
         <v>31</v>
       </c>
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="100" t="s">
+      <c r="C34" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="D34" s="100" t="s">
+      <c r="D34" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="113" t="s">
+      <c r="E34" s="105" t="s">
         <v>141</v>
       </c>
-      <c r="F34" s="128" t="s">
+      <c r="F34" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="G34" s="112" t="s">
+      <c r="G34" s="104" t="s">
         <v>142</v>
       </c>
-      <c r="H34" s="113" t="s">
+      <c r="H34" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="I34" s="114" t="s">
+      <c r="I34" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="J34" s="120">
+      <c r="J34" s="112">
         <f>IF(H34="NA","NA",IF(H34="Critical",-10,IF(H34="Yes",10,IF(I34=1,-2,IF(I34=2,-4,IF(I34=3,-6,IF(I34=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
-      <c r="K34" s="57"/>
-      <c r="L34" s="76" t="s">
+      <c r="K34" s="49"/>
+      <c r="L34" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="M34" s="67"/>
-      <c r="N34" s="68"/>
-      <c r="O34" s="59"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="51"/>
-    </row>
-    <row r="35" spans="1:17" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A35" s="84">
+      <c r="M34" s="59"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+    </row>
+    <row r="35" spans="1:17" s="66" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="76">
         <v>32</v>
       </c>
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="100" t="s">
+      <c r="C35" s="92" t="s">
         <v>143</v>
       </c>
-      <c r="D35" s="100" t="s">
+      <c r="D35" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="100" t="s">
+      <c r="E35" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="F35" s="126" t="s">
+      <c r="F35" s="118" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100" t="s">
+      <c r="G35" s="92"/>
+      <c r="H35" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="I35" s="100" t="s">
+      <c r="I35" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="J35" s="121" t="s">
+      <c r="J35" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="73" t="s">
+      <c r="K35" s="49"/>
+      <c r="L35" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="M35" s="67"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-    </row>
-    <row r="36" spans="1:17" s="66" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="87" t="s">
+      <c r="M35" s="59"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
+    </row>
+    <row r="36" spans="1:17" s="58" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77" t="s">
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="122">
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="114">
         <f>(SUM(J27:J35)/(COUNT(J27:J35)*10)*20)</f>
         <v>20</v>
       </c>
-      <c r="K36" s="79"/>
-      <c r="L36" s="77"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="80"/>
-      <c r="O36" s="81"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="69"/>
+      <c r="M36" s="69"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="73"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="75"/>
     </row>
   </sheetData>
   <dataValidations count="10">
@@ -3844,304 +3860,307 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB522AB-16D4-4166-B7FB-DF53DD5B0AF8}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="135" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.3984375" style="135" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.8984375" style="135" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="135" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.8984375" style="135" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="30.59765625" style="135" customWidth="1"/>
-    <col min="8" max="8" width="56" style="135" customWidth="1"/>
-    <col min="9" max="9" width="44.5" style="135" customWidth="1"/>
-    <col min="10" max="10" width="16.59765625" style="135" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="135" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.3984375" style="135" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.19921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.69921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.69921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.8984375" style="135" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.19921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.69921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.59765625" style="135" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.5" style="135" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.09765625" style="135" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5" style="135" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.69921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.19921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.5" style="135" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.69921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.19921875" style="135" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="23" style="135" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="135"/>
+    <col min="1" max="1" width="14" style="127" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" style="127" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.8984375" style="127" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="127" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.8984375" style="127" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="30.59765625" style="127" customWidth="1"/>
+    <col min="8" max="8" width="56" style="127" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="127" customWidth="1"/>
+    <col min="10" max="10" width="16.59765625" style="127" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="127" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.3984375" style="127" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.19921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.69921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.69921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.8984375" style="127" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.19921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.69921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.59765625" style="127" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.5" style="127" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.09765625" style="127" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5" style="127" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.69921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.19921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.5" style="127" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.69921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.19921875" style="127" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23" style="127" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="127"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="131" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:29" s="123" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="132" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="121" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="129" t="s">
+      <c r="C1" s="121" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="D1" s="121" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="129" t="s">
+      <c r="E1" s="121" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="129" t="s">
+      <c r="F1" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="129" t="s">
+      <c r="G1" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="129" t="s">
+      <c r="H1" s="121" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="129" t="s">
+      <c r="I1" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="129" t="s">
+      <c r="J1" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="J1" s="129" t="s">
+      <c r="K1" s="121" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="129" t="s">
+      <c r="L1" s="121" t="s">
         <v>153</v>
       </c>
-      <c r="L1" s="129" t="s">
+      <c r="M1" s="121" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="129" t="s">
+      <c r="N1" s="121" t="s">
         <v>155</v>
       </c>
-      <c r="N1" s="129" t="s">
+      <c r="O1" s="121" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="129" t="s">
+      <c r="P1" s="121" t="s">
         <v>157</v>
       </c>
-      <c r="P1" s="130" t="s">
+      <c r="Q1" s="122" t="s">
         <v>158</v>
       </c>
-      <c r="Q1" s="129" t="s">
+      <c r="R1" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="R1" s="129" t="s">
+      <c r="S1" s="121" t="s">
         <v>160</v>
       </c>
-      <c r="S1" s="129" t="s">
+      <c r="T1" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="T1" s="129" t="s">
+      <c r="U1" s="121" t="s">
         <v>162</v>
       </c>
-      <c r="U1" s="129" t="s">
+      <c r="V1" s="121" t="s">
         <v>163</v>
       </c>
-      <c r="V1" s="129" t="s">
+      <c r="W1" s="121" t="s">
         <v>164</v>
       </c>
-      <c r="W1" s="129" t="s">
+      <c r="X1" s="121" t="s">
         <v>165</v>
       </c>
-      <c r="X1" s="129" t="s">
+      <c r="Y1" s="121" t="s">
         <v>166</v>
       </c>
-      <c r="Y1" s="129" t="s">
+      <c r="Z1" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="Z1" s="129" t="s">
+      <c r="AA1" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AA1" s="129" t="s">
+      <c r="AB1" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="AB1" s="129" t="s">
+      <c r="AC1" s="121" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="132"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="133"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
-      <c r="U2" s="133"/>
-      <c r="V2" s="133"/>
-      <c r="W2" s="133"/>
-      <c r="X2" s="133"/>
-      <c r="Y2" s="133"/>
-      <c r="Z2" s="133"/>
-      <c r="AA2" s="133"/>
-      <c r="AB2" s="133"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="132"/>
-      <c r="B3" s="132"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="133"/>
-      <c r="S3" s="133"/>
-      <c r="T3" s="133"/>
-      <c r="U3" s="133"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
-      <c r="Z3" s="133"/>
-      <c r="AA3" s="133"/>
-      <c r="AB3" s="133"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="132"/>
-      <c r="B4" s="132"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
-      <c r="S4" s="133"/>
-      <c r="T4" s="133"/>
-      <c r="U4" s="133"/>
-      <c r="V4" s="133"/>
-      <c r="W4" s="133"/>
-      <c r="X4" s="133"/>
-      <c r="Y4" s="133"/>
-      <c r="Z4" s="133"/>
-      <c r="AA4" s="133"/>
-      <c r="AB4" s="133"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="132"/>
-      <c r="B5" s="132"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="133"/>
-      <c r="T5" s="133"/>
-      <c r="U5" s="133"/>
-      <c r="V5" s="133"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="133"/>
-      <c r="Y5" s="133"/>
-      <c r="Z5" s="133"/>
-      <c r="AA5" s="133"/>
-      <c r="AB5" s="133"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="132"/>
-      <c r="B6" s="132"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-      <c r="K6" s="133"/>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-      <c r="N6" s="133"/>
-      <c r="O6" s="133"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="133"/>
-      <c r="R6" s="133"/>
-      <c r="S6" s="133"/>
-      <c r="T6" s="133"/>
-      <c r="U6" s="133"/>
-      <c r="V6" s="133"/>
-      <c r="W6" s="133"/>
-      <c r="X6" s="133"/>
-      <c r="Y6" s="133"/>
-      <c r="Z6" s="133"/>
-      <c r="AA6" s="133"/>
-      <c r="AB6" s="133"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="132"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="133"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="133"/>
-      <c r="X7" s="133"/>
-      <c r="Y7" s="133"/>
-      <c r="Z7" s="133"/>
-      <c r="AA7" s="133"/>
-      <c r="AB7" s="133"/>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="124"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="125"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="124"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="125"/>
+      <c r="Y3" s="125"/>
+      <c r="Z3" s="125"/>
+      <c r="AA3" s="125"/>
+      <c r="AB3" s="125"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="126"/>
+      <c r="Q4" s="125"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="125"/>
+      <c r="T4" s="125"/>
+      <c r="U4" s="125"/>
+      <c r="V4" s="125"/>
+      <c r="W4" s="125"/>
+      <c r="X4" s="125"/>
+      <c r="Y4" s="125"/>
+      <c r="Z4" s="125"/>
+      <c r="AA4" s="125"/>
+      <c r="AB4" s="125"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="124"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="126"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="125"/>
+      <c r="W5" s="125"/>
+      <c r="X5" s="125"/>
+      <c r="Y5" s="125"/>
+      <c r="Z5" s="125"/>
+      <c r="AA5" s="125"/>
+      <c r="AB5" s="125"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="124"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="125"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="125"/>
+      <c r="S6" s="125"/>
+      <c r="T6" s="125"/>
+      <c r="U6" s="125"/>
+      <c r="V6" s="125"/>
+      <c r="W6" s="125"/>
+      <c r="X6" s="125"/>
+      <c r="Y6" s="125"/>
+      <c r="Z6" s="125"/>
+      <c r="AA6" s="125"/>
+      <c r="AB6" s="125"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="124"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="125"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="125"/>
+      <c r="X7" s="125"/>
+      <c r="Y7" s="125"/>
+      <c r="Z7" s="125"/>
+      <c r="AA7" s="125"/>
+      <c r="AB7" s="125"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
